--- a/Document/TR-1um_GDSII_Table.xlsx
+++ b/Document/TR-1um_GDSII_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Library/CloudStorage/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1909266-F903-8246-A144-BCB170806AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93241D01-FF07-6547-AF3F-FDD938CAE927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="760" windowWidth="29400" windowHeight="18600" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
@@ -293,12 +293,6 @@
     <t>DLBGRR</t>
   </si>
   <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>POLY resistor</t>
-  </si>
-  <si>
     <t>Active for capacitance</t>
   </si>
   <si>
@@ -332,9 +326,6 @@
     <t>In the reference manual, design rule defined to XXXX that recognized by DLXXXX</t>
   </si>
   <si>
-    <t>POLY transistor</t>
-  </si>
-  <si>
     <t>Active for resistor</t>
   </si>
   <si>
@@ -344,7 +335,16 @@
     <t>Measurement region</t>
   </si>
   <si>
-    <t>PO</t>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>Gate POLY resistor</t>
+  </si>
+  <si>
+    <t>Gate Poly transistor</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M8" s="5"/>
     </row>
@@ -1421,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M9" s="5"/>
     </row>
@@ -1439,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M10" s="5"/>
     </row>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1700,7 +1700,7 @@
       <c r="C22" s="12"/>
       <c r="E22" s="15"/>
       <c r="G22" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H22" s="1">
         <v>8</v>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M22" s="5"/>
     </row>
@@ -1718,7 +1718,7 @@
       <c r="C23" s="12"/>
       <c r="E23" s="15"/>
       <c r="G23" s="12" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
         <v>8</v>
@@ -1727,7 +1727,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M23" s="5"/>
     </row>
@@ -2010,7 +2010,7 @@
     <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="54"/>
       <c r="C36" s="55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" s="56">
         <v>48</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F36" s="56"/>
       <c r="G36" s="55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H36" s="56">
         <v>48</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="J36" s="56"/>
       <c r="K36" s="58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L36" s="56"/>
       <c r="M36" s="59"/>
@@ -2094,7 +2094,7 @@
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" s="54"/>
       <c r="C39" s="55" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D39" s="56">
         <v>63</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F39" s="56"/>
       <c r="G39" s="55" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H39" s="56">
         <v>63</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="J39" s="56"/>
       <c r="K39" s="58" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L39" s="56"/>
       <c r="M39" s="59"/>
@@ -2122,7 +2122,7 @@
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" s="54"/>
       <c r="C40" s="55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D40" s="56">
         <v>80</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="F40" s="56"/>
       <c r="G40" s="55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H40" s="56">
         <v>80</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="J40" s="56"/>
       <c r="K40" s="58" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L40" s="56"/>
       <c r="M40" s="59"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L45" s="21"/>
       <c r="M45" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="60" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.2">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="60" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.2">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="60" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
@@ -2365,7 +2365,7 @@
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D51" s="1">
         <v>154</v>
@@ -2674,12 +2674,12 @@
         <v>81</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="2:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="C67" s="61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Document/TR-1um_GDSII_Table.xlsx
+++ b/Document/TR-1um_GDSII_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/okamura/Library/CloudStorage/Dropbox/91_OpenPDK/TR-1um/Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93241D01-FF07-6547-AF3F-FDD938CAE927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB07B079-2974-9842-AB36-D3B33B28C33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="760" windowWidth="29400" windowHeight="18600" xr2:uid="{7F1200E8-B51D-9446-A5CE-CEA05B5231B7}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>V1</t>
   </si>
   <si>
-    <t>PE</t>
-  </si>
-  <si>
     <t>ESD PMOS channel</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
   </si>
   <si>
     <t>Gate Poly transistor</t>
+  </si>
+  <si>
+    <t>PO</t>
   </si>
 </sst>
 </file>
@@ -1252,13 +1252,13 @@
     <row r="2" spans="2:13" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="B2" s="28"/>
       <c r="C2" s="63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
       <c r="F2" s="29"/>
       <c r="G2" s="66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2" s="67"/>
       <c r="I2" s="68"/>
@@ -1270,23 +1270,23 @@
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B3" s="31"/>
       <c r="C3" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="E3" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="I3" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>69</v>
       </c>
       <c r="J3" s="32"/>
       <c r="K3" s="32"/>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" s="11">
         <v>140</v>
@@ -1336,7 +1336,7 @@
       <c r="I5" s="44"/>
       <c r="J5" s="43"/>
       <c r="K5" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L5" s="46"/>
       <c r="M5" s="47"/>
@@ -1360,7 +1360,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="43"/>
       <c r="K6" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L6" s="46"/>
       <c r="M6" s="47"/>
@@ -1384,7 +1384,7 @@
       <c r="I7" s="44"/>
       <c r="J7" s="43"/>
       <c r="K7" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L7" s="46"/>
       <c r="M7" s="47"/>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M8" s="5"/>
     </row>
@@ -1421,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M9" s="5"/>
     </row>
@@ -1439,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M10" s="5"/>
     </row>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1480,7 +1480,7 @@
       <c r="I12" s="44"/>
       <c r="J12" s="43"/>
       <c r="K12" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L12" s="46"/>
       <c r="M12" s="47"/>
@@ -1504,7 +1504,7 @@
       <c r="I13" s="44"/>
       <c r="J13" s="43"/>
       <c r="K13" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L13" s="46"/>
       <c r="M13" s="47"/>
@@ -1528,7 +1528,7 @@
       <c r="I14" s="44"/>
       <c r="J14" s="43"/>
       <c r="K14" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L14" s="46"/>
       <c r="M14" s="47"/>
@@ -1552,7 +1552,7 @@
       <c r="I15" s="51"/>
       <c r="J15" s="50"/>
       <c r="K15" s="52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L15" s="50"/>
       <c r="M15" s="53"/>
@@ -1576,7 +1576,7 @@
       <c r="I16" s="51"/>
       <c r="J16" s="50"/>
       <c r="K16" s="52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L16" s="50"/>
       <c r="M16" s="53"/>
@@ -1600,7 +1600,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="43"/>
       <c r="K17" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L17" s="46"/>
       <c r="M17" s="47"/>
@@ -1624,7 +1624,7 @@
       <c r="I18" s="44"/>
       <c r="J18" s="43"/>
       <c r="K18" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L18" s="46"/>
       <c r="M18" s="47"/>
@@ -1648,7 +1648,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="43"/>
       <c r="K19" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L19" s="46"/>
       <c r="M19" s="47"/>
@@ -1672,7 +1672,7 @@
       <c r="I20" s="51"/>
       <c r="J20" s="50"/>
       <c r="K20" s="52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L20" s="50"/>
       <c r="M20" s="53"/>
@@ -1700,7 +1700,7 @@
       <c r="C22" s="12"/>
       <c r="E22" s="15"/>
       <c r="G22" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H22" s="1">
         <v>8</v>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M22" s="5"/>
     </row>
@@ -1718,7 +1718,7 @@
       <c r="C23" s="12"/>
       <c r="E23" s="15"/>
       <c r="G23" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H23" s="1">
         <v>8</v>
@@ -1727,7 +1727,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M23" s="5"/>
     </row>
@@ -1750,7 +1750,7 @@
       <c r="I24" s="44"/>
       <c r="J24" s="43"/>
       <c r="K24" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L24" s="46"/>
       <c r="M24" s="47"/>
@@ -1774,7 +1774,7 @@
       <c r="I25" s="44"/>
       <c r="J25" s="43"/>
       <c r="K25" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L25" s="46"/>
       <c r="M25" s="47"/>
@@ -1798,7 +1798,7 @@
       <c r="I26" s="44"/>
       <c r="J26" s="43"/>
       <c r="K26" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L26" s="46"/>
       <c r="M26" s="47"/>
@@ -1822,7 +1822,7 @@
       <c r="I27" s="44"/>
       <c r="J27" s="43"/>
       <c r="K27" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L27" s="46"/>
       <c r="M27" s="47"/>
@@ -1846,7 +1846,7 @@
       <c r="I28" s="44"/>
       <c r="J28" s="43"/>
       <c r="K28" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L28" s="46"/>
       <c r="M28" s="47"/>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="H33" s="1">
         <v>14</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="J35" s="56"/>
       <c r="K35" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L35" s="56"/>
       <c r="M35" s="59"/>
@@ -2010,7 +2010,7 @@
     <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="54"/>
       <c r="C36" s="55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D36" s="56">
         <v>48</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F36" s="56"/>
       <c r="G36" s="55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H36" s="56">
         <v>48</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="J36" s="56"/>
       <c r="K36" s="58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L36" s="56"/>
       <c r="M36" s="59"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J37" s="56"/>
       <c r="K37" s="58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L37" s="56"/>
       <c r="M37" s="59"/>
@@ -2066,7 +2066,7 @@
     <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B38" s="54"/>
       <c r="C38" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="56">
         <v>63</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F38" s="56"/>
       <c r="G38" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H38" s="56">
         <v>63</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J38" s="56"/>
       <c r="K38" s="58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L38" s="56"/>
       <c r="M38" s="59"/>
@@ -2094,7 +2094,7 @@
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" s="54"/>
       <c r="C39" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" s="56">
         <v>63</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F39" s="56"/>
       <c r="G39" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H39" s="56">
         <v>63</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="J39" s="56"/>
       <c r="K39" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L39" s="56"/>
       <c r="M39" s="59"/>
@@ -2122,7 +2122,7 @@
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" s="54"/>
       <c r="C40" s="55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" s="56">
         <v>80</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="F40" s="56"/>
       <c r="G40" s="55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H40" s="56">
         <v>80</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="J40" s="56"/>
       <c r="K40" s="58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L40" s="56"/>
       <c r="M40" s="59"/>
@@ -2150,7 +2150,7 @@
     <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41" s="54"/>
       <c r="C41" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D41" s="56">
         <v>235</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F41" s="56"/>
       <c r="G41" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H41" s="56">
         <v>235</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J41" s="56"/>
       <c r="K41" s="58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L41" s="56"/>
       <c r="M41" s="59"/>
@@ -2186,7 +2186,7 @@
     <row r="43" spans="2:13" ht="22" x14ac:dyDescent="0.2">
       <c r="B43" s="23"/>
       <c r="C43" s="69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D43" s="70"/>
       <c r="E43" s="71"/>
@@ -2202,13 +2202,13 @@
     <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B44" s="34"/>
       <c r="C44" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D44" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="37" t="s">
         <v>68</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>69</v>
       </c>
       <c r="F44" s="36"/>
       <c r="G44" s="35"/>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B45" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>36</v>
@@ -2238,16 +2238,16 @@
       <c r="I45" s="22"/>
       <c r="J45" s="21"/>
       <c r="K45" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L45" s="21"/>
       <c r="M45" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B46" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>35</v>
@@ -2263,16 +2263,16 @@
       <c r="I46" s="17"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B47" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>34</v>
@@ -2288,19 +2288,19 @@
       <c r="I47" s="17"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="1">
         <v>119</v>
@@ -2313,17 +2313,17 @@
       <c r="I48" s="17"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
       <c r="C49" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" s="1">
         <v>150</v>
@@ -2336,7 +2336,7 @@
       <c r="I49" s="17"/>
       <c r="J49" s="6"/>
       <c r="K49" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="5"/>
@@ -2344,7 +2344,7 @@
     <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50" s="4"/>
       <c r="C50" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" s="1">
         <v>151</v>
@@ -2357,7 +2357,7 @@
       <c r="I50" s="17"/>
       <c r="J50" s="6"/>
       <c r="K50" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="5"/>
@@ -2365,7 +2365,7 @@
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="1">
         <v>154</v>
@@ -2378,14 +2378,14 @@
       <c r="I51" s="17"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="5"/>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>24</v>
@@ -2401,14 +2401,14 @@
       <c r="I52" s="17"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="5"/>
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B53" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>25</v>
@@ -2424,17 +2424,17 @@
       <c r="I53" s="17"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="5"/>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54" s="1">
         <v>162</v>
@@ -2447,14 +2447,14 @@
       <c r="I54" s="17"/>
       <c r="J54" s="6"/>
       <c r="K54" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="5"/>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>37</v>
@@ -2470,7 +2470,7 @@
       <c r="I55" s="17"/>
       <c r="J55" s="6"/>
       <c r="K55" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="5"/>
@@ -2491,17 +2491,17 @@
       <c r="I56" s="17"/>
       <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="5"/>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="1">
         <v>167</v>
@@ -2514,14 +2514,14 @@
       <c r="I57" s="17"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="5"/>
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B58" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>27</v>
@@ -2537,14 +2537,14 @@
       <c r="I58" s="17"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="5"/>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B59" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>33</v>
@@ -2560,14 +2560,14 @@
       <c r="I59" s="17"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L59" s="6"/>
       <c r="M59" s="5"/>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B60" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>32</v>
@@ -2583,14 +2583,14 @@
       <c r="I60" s="17"/>
       <c r="J60" s="6"/>
       <c r="K60" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="5"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>28</v>
@@ -2606,14 +2606,14 @@
       <c r="I61" s="17"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="5"/>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>29</v>
@@ -2629,7 +2629,7 @@
       <c r="I62" s="17"/>
       <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L62" s="6"/>
       <c r="M62" s="5"/>
@@ -2637,7 +2637,7 @@
     <row r="63" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B63" s="4"/>
       <c r="C63" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D63" s="1">
         <v>182</v>
@@ -2650,7 +2650,7 @@
       <c r="I63" s="17"/>
       <c r="J63" s="6"/>
       <c r="K63" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L63" s="6"/>
       <c r="M63" s="5"/>
@@ -2671,15 +2671,15 @@
     </row>
     <row r="66" spans="2:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="2:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="C67" s="61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
